--- a/artfynd/A 32797-2025 artfynd.xlsx
+++ b/artfynd/A 32797-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126521596</v>
+        <v>126521570</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>91241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588866</v>
+        <v>588845</v>
       </c>
       <c r="R3" t="n">
-        <v>7293503</v>
+        <v>7293398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126521570</v>
+        <v>126521596</v>
       </c>
       <c r="B4" t="n">
-        <v>91241</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588845</v>
+        <v>588866</v>
       </c>
       <c r="R4" t="n">
-        <v>7293398</v>
+        <v>7293503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 32797-2025 artfynd.xlsx
+++ b/artfynd/A 32797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126521587</v>
+        <v>126521544</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588666</v>
+        <v>588687</v>
       </c>
       <c r="R2" t="n">
-        <v>7293308</v>
+        <v>7293189</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,7 +784,7 @@
         <v>126521570</v>
       </c>
       <c r="B3" t="n">
-        <v>91241</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126521596</v>
+        <v>126521536</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588866</v>
+        <v>588654</v>
       </c>
       <c r="R4" t="n">
-        <v>7293503</v>
+        <v>7293009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126521497</v>
+        <v>126521554</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588674</v>
+        <v>588659</v>
       </c>
       <c r="R5" t="n">
-        <v>7293144</v>
+        <v>7293204</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126521536</v>
+        <v>126521497</v>
       </c>
       <c r="B6" t="n">
-        <v>80084</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588654</v>
+        <v>588674</v>
       </c>
       <c r="R6" t="n">
-        <v>7293009</v>
+        <v>7293144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1208,7 @@
         <v>126521560</v>
       </c>
       <c r="B7" t="n">
-        <v>75075</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126521544</v>
+        <v>126521587</v>
       </c>
       <c r="B8" t="n">
-        <v>91241</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1322,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,13 +1358,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588687</v>
+        <v>588666</v>
       </c>
       <c r="R8" t="n">
-        <v>7293189</v>
+        <v>7293308</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,7 +1402,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1422,218 +1422,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>126521554</v>
-      </c>
-      <c r="B9" t="n">
-        <v>80084</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bergtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>588659</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7293204</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik och lågproduktiv grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>126521576</v>
-      </c>
-      <c r="B10" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Bergtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>588869</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7293423</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Luckig, lövrik och lågproduktiv grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32797-2025 artfynd.xlsx
+++ b/artfynd/A 32797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521536</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521554</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521560</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,8 +1457,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126521587</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>